--- a/extenbooks/S601.xlsx
+++ b/extenbooks/S601.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S601.xlsx
+++ b/extenbooks/S601.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -958,54 +958,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S601-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S601 — Personal Tax Workers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `personal_income_tax_workers`</t>
+          <t># S601 — Personal Tax Workers</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `personal_income_tax_workers`</t>
         </is>
       </c>
     </row>
@@ -1021,31 +1022,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Personal income taxes paid by workers (the working class, per S&amp;T's class decomposition of NIPA tables).</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1066,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Personal income taxes paid by workers (the working class, per S&amp;T's class decomposition of NIPA tables).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1078,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1090,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1102,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1114,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1126,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=22.78B; 1989=385.73B; ÷1000 from MILLIONS in source</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1138,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S601_personal_tax_workers.py`. Both endpoints PASS.</t>
+          <t>1952=22.78B; 1989=385.73B; ÷1000 from MILLIONS in source</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1150,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S601_personal_tax_workers.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1153,23 +1162,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S601_personal_tax_workers.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1182,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S601.csv</t>
+          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1190,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S601_personal_tax_workers.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S601_personal_tax_workers.py</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1198,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S601.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S601.csv</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1206,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S601_personal_tax_workers.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S601_personal_tax_workers.py</t>
         </is>
       </c>
     </row>
@@ -1209,19 +1214,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S601.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S601_personal_tax_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1242,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1254,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1256,6 +1265,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1272,12 +1293,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1300,179 +1321,278 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Personal income tax allocated to workers using income-proportional method: S601 = Personal income tax × (W / total personal income). W is employee compensation; total personal income is from NIPA Table 2.1. This yields the worker share of federal + state/local personal income taxes.</t>
+          <t>Group II - Personal taxes (workers' share = labor income/personal income): Personal income taxes (federal and state); Motor vehicle licenses; Property taxes (primarily on homes - adjusted for homeowners only); Other taxes and nontaxes (passport fees, fines, etc. - very small).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N, Tax Classification, Group II</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Federal personal income tax from NIPA Table 3.2 (Federal Government Current Receipts). State/local personal income tax from NIPA Table 3.3 (State and Local Government Current Receipts, line 9). Worker compensation (W) and total personal income from NIPA Table 2.1.</t>
+          <t>Excluded taxes (not levied on workers): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Tables 2.1, 3.2, 3.3</t>
+          <t>ST_1994, Appendix N, Footnote 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 6.4 plots per-worker tax burden alongside per-worker benefits, showing that personal income taxes are the largest single tax component for workers, growing from roughly 0.18 of employee compensation in 1952 to 0.32 by 1989.</t>
+          <t>Personal income taxes (federal + state) 1964: total 50.0, labor share applied = 0.727, labor portion 36.4 (billions of $).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Fig 6.4; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Table N.1, Taxes Group II row</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The income-proportional allocation assumes workers pay taxes in proportion to their share of total personal income. This is a simplification: progressive rate structures mean workers may pay a lower effective rate than capitalists. Shaikh &amp; Tonak argue this is acceptable because workers also receive less capital income, and the two effects partially offset.</t>
+          <t>Labor share 1964: 0.727 (labor income / personal income).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6 methodology section</t>
+          <t>ST_1994, Appendix N, Table N.1 data sources note</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cross_study_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Moos (2017) uses the same income-proportional method for personal tax allocation. Tonak benchmark data confirms close agreement on this component. The AS2 extension also uses W/personal_income from BEA NIPA for post-1989 allocation.</t>
+          <t>Group II - Personal taxes (workers' share = labor income/personal income): Personal income taxes (federal and state); Motor vehicle licenses; Property taxes (primarily on homes - adjusted for homeowners only); Other taxes and nontaxes (passport fees, fines, etc. - very small).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moos_2017; nsw_comparison_benchmarks.csv</t>
+          <t>ST_1994, Appendix N (Tax Classification, Group II); KB chunk_38 lines 262-266</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-008 (2026-04-09): Income-proportional tax allocation method confirmed correct. HDARP extraction of Section 3.3 (pages 63-65) documents the net royalty framework: NRYwp = net taxes on productive workers. Book quote p.64: 'The true measure of variable capital is the nominal wage of productive workers minus any net royalty payments made by them.' P09 implementation verified.</t>
+          <t>Excluded taxes (not levied on workers): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994, Appendix N footnote 2; KB chunk_38 lines 268-271</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Personal income taxes (federal + state) 1964: total 50.0, labor share applied = 0.727, labor portion 36.4 (billions of $).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 (Taxes, Group II); KB chunk_38 line 302</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Worker share of personal income taxes allocated via income-proportional method (W/total personal income) applied to combined federal + state/local personal income tax revenue from NIPA Tables 3.2 and 3.3. Method confirmed by DEC-008 against book Section 3.3 NRYwp framework.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Group II (labor share = labor income/personal income) applies to Education; Health and hospitals; Recreational and cultural activities; Energy; Natural resources; Transportation (adjusted by gas share of passenger cars); Postal services.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group II); KB chunk_38 lines 226-233</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Labor share 1964: 0.727 (labor income / personal income).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Table N.1 data sources); KB chunk_38 line 321</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Personal income tax allocated to workers using income-proportional method: S601 = Personal income tax × (W / total personal income). W is employee compensation; total personal income is from NIPA Table 2.1. This yields the worker share of federal + state/local personal income taxes.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Income-proportional allocation ignores progressive rate structure</t>
+          <t>Federal personal income tax from NIPA Table 3.2 (Federal Government Current Receipts). State/local personal income tax from NIPA Table 3.3 (State and Local Government Current Receipts, line 9). Worker compensation (W) and total personal income from NIPA Table 2.1.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEA NIPA Tables 2.1, 3.2, 3.3</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Does not distinguish between wage income tax and capital gains tax within personal income tax</t>
+          <t>Fig 6.4 plots per-worker tax burden alongside per-worker benefits, showing that personal income taxes are the largest single tax component for workers, growing from roughly 0.18 of employee compensation in 1952 to 0.32 by 1989.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_1994, Fig 6.4; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>State/local income tax structures vary significantly across states</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>The income-proportional allocation assumes workers pay taxes in proportion to their share of total personal income. This is a simplification: progressive rate structures mean workers may pay a lower effective rate than capitalists. Shaikh &amp; Tonak argue this is acceptable because workers also receive less capital income, and the two effects partially offset.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6 methodology section</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_study_comparison</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Moos (2017) uses the same income-proportional method for personal tax allocation. Tonak benchmark data confirms close agreement on this component. The AS2 extension also uses W/personal_income from BEA NIPA for post-1989 allocation.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Moos_2017; nsw_comparison_benchmarks.csv</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S602</t>
-        </is>
-      </c>
-    </row>
+          <t>decision_log_note</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09): Income-proportional tax allocation method confirmed correct. HDARP extraction of Section 3.3 (pages 63-65) documents the net royalty framework: NRYwp = net taxes on productive workers. Book quote p.64: 'The true measure of variable capital is the nominal wage of productive workers minus any net royalty payments made by them.' P09 implementation verified.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S603</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>Group II - Personal taxes (workers' share = labor income/personal income): Personal income taxes (federal and state); Motor vehicle licenses; Property taxes (primarily on homes - adjusted for homeowners only); Other taxes and nontaxes (passport fees, fines, etc. - very small).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group II); KB chunk_38 lines 262-266</t>
         </is>
       </c>
     </row>
@@ -1480,49 +1600,178 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S607</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+          <t>Excluded taxes (not levied on workers): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N footnote 2; KB chunk_38 lines 268-271</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Personal income taxes (federal + state) 1964: total 50.0, labor share applied = 0.727, labor portion 36.4 (billions of $).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 (Taxes, Group II); KB chunk_38 line 302</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>citations:</t>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Group II (labor share = labor income/personal income) applies to Education; Health and hospitals; Recreational and cultural activities; Energy; Natural resources; Transportation (adjusted by gas share of passenger cars); Postal services.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group II); KB chunk_38 lines 226-233</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ST_1994</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BEA_NIPA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
-        </is>
-      </c>
-    </row>
+          <t>Labor share 1964: 0.727 (labor income / personal income).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Table N.1 data sources); KB chunk_38 line 321</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worker share of personal income taxes allocated via income-proportional method (W/total personal income) applied to combined federal + state/local personal income tax revenue from NIPA Tables 3.2 and 3.3. Method confirmed by [internal-decision-record] against book Section 3.3 NRYwp framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Income-proportional allocation ignores progressive rate structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Does not distinguish between wage income tax and capital gains tax within personal income tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>State/local income tax structures vary significantly across states</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S602</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S603</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BEA_NIPA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Moos, Julie. 2017. The Net Social Wage in the United States, 1952-2012. PhD dissertation.</t>
         </is>
@@ -1539,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1602,7 +1851,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1872,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 22.7849, "1989": 385.7297}</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1896,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
